--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/21062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/21062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domingo, 21 de junio de 2026
-*Evangelio del Día*
-Lectura del santo Evangelio según san Mateo
-Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
-*Oración de la mañana*
-Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
-Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
-Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
-En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>domingo, 21 de junio de 2026
+*Evangelio del Día*
+Lectura del santo Evangelio según san Mateo
+Mateo 10, 26-33 En aquel tiempo, Jesús dijo a sus apóstoles: "No teman a los hombres. No hay nada oculto que no llegue a descubrirse; no hay nada secreto que no llegue a saberse. Lo que les digo de noche, repítanlo en pleno día, y lo que les digo al oído, pregónenlo desde las azoteas. No tengan miedo a los que matan el cuerpo, pero no pueden matar el alma. Teman, más bien, a quien puede arrojar al lugar de castigo el alma y el cuerpo. ¿No es verdad que se venden dos pajarillos por una moneda? Sin embargo, ni uno solo de ellos cae por tierra si no lo permite el Padre. En cuanto a ustedes, hasta los cabellos de su cabeza están contados. Por lo tanto, no tengan miedo, porque ustedes valen mucho más que todos los pájaros del mundo. A quien me reconozca delante de los hombres, yo también lo reconoceré ante mi Padre, que está en los cielos; pero al que me niegue delante de los hombres, yo también lo negaré ante mi Padre, que está en los cielos".
+*Oración de la mañana*
+Amado Jesús, que nos enseñas a no temer, a tener valentía en la verdad y a expresarla sin miedo, ayúdanos a vivir según tus palabras, a repetir tus enseñanzas día tras día, y a proclamar tu amor desde las alturas. Bríndanos la fuerza para reconocerte ante los hombres, sabiendo que así seremos reconocidos ante el Padre.
+Padre bondadoso, agradecemos por este nuevo día, por el aire que respiramos, por la vida que nos has otorgado. Nos maravillamos de tu cuidado detallado, pues hasta los cabellos de nuestra cabeza están contados por ti. Ayúdanos a recordar siempre que somos valiosos a tus ojos, mucho más que todos los pájaros del mundo. Danos un corazón valiente para resistir a quienes buscan dañar nuestras almas.
+Espíritu Santo, te pedimos que nos guíes en este día, que nuestras acciones sean reflejo de tu amor y verdad. Ilumina nuestro camino y permítenos ser la luz en la oscuridad, mostrando a los demás el amor y la misericordia de la Trinidad Sagrada.
+En la confianza de ser hijos del Dios vivo, comenzamos este día con alegría y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>